--- a/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
+++ b/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>107 (4.53%)</t>
+          <t>108 (4.58%)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>638 (27.03%)</t>
+          <t>637 (26.99%)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1439 (60.98%)</t>
+          <t>1439 (60.97%)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>110 (4.66%)</t>
+          <t>111 (4.70%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>550 (23.30%)</t>
+          <t>549 (23.26%)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>19 (0.81%)</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>79 (3.35%)</t>
+          <t>78 (3.30%)</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>9 (0.38%)</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>29 (1.23%)</t>
+          <t>30 (1.27%)</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>101 (4.28%)</t>
+          <t>100 (4.24%)</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>19 (0.81%)</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>79 (3.35%)</t>
+          <t>78 (3.30%)</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -11593,7 +11593,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -11605,25 +11605,25 @@
         <v>18</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>1.5371</v>
+        <v>1.5306</v>
       </c>
       <c r="H3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>5.2092</v>
+        <v>5.2721</v>
       </c>
       <c r="J3" t="n">
         <v>21</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>1.7933</v>
+        <v>1.7857</v>
       </c>
       <c r="L3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>28.0102</v>
+        <v>27.9762</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -11632,10 +11632,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>63.45</v>
+        <v>63.4354</v>
       </c>
     </row>
     <row r="4">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -11662,25 +11662,25 @@
         <v>1</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.8621</v>
+        <v>0.9091</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>2.5862</v>
+        <v>2.7273</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>5.1724</v>
+        <v>5.4545</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>26.7241</v>
+        <v>26.3636</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -11689,10 +11689,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>64.65519999999999</v>
+        <v>64.5455</v>
       </c>
     </row>
     <row r="5">
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11719,25 +11719,25 @@
         <v>39</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5.5398</v>
+        <v>5.5319</v>
       </c>
       <c r="H5" t="n">
         <v>25</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>3.5511</v>
+        <v>3.5461</v>
       </c>
       <c r="J5" t="n">
         <v>44</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>6.25</v>
+        <v>6.2411</v>
       </c>
       <c r="L5" t="n">
         <v>186</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>26.4205</v>
+        <v>26.383</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -11746,10 +11746,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>58.2386</v>
+        <v>58.2979</v>
       </c>
     </row>
     <row r="6">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -11896,19 +11896,19 @@
         <v>11</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.9394</v>
+        <v>0.9354</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.3416</v>
+        <v>0.3401</v>
       </c>
       <c r="L8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>10.9308</v>
+        <v>10.9694</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -11917,10 +11917,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>87.7882</v>
+        <v>87.7551</v>
       </c>
     </row>
     <row r="9">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.8621</v>
+        <v>0.9091</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11962,10 +11962,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>12.931</v>
+        <v>12.7273</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -11974,10 +11974,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>86.2069</v>
+        <v>86.36360000000001</v>
       </c>
     </row>
     <row r="10">
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -12004,25 +12004,25 @@
         <v>5</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.5682</v>
+        <v>0.5674</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>45</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>6.392</v>
+        <v>6.383</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -12031,10 +12031,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>91.6193</v>
+        <v>91.63120000000001</v>
       </c>
     </row>
     <row r="11">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -12175,25 +12175,25 @@
         <v>17</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>1.4518</v>
+        <v>1.4456</v>
       </c>
       <c r="H13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>6.234</v>
+        <v>6.2925</v>
       </c>
       <c r="J13" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1.7079</v>
+        <v>1.7007</v>
       </c>
       <c r="L13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>25.2775</v>
+        <v>25.2551</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -12202,10 +12202,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>65.3288</v>
+        <v>65.3061</v>
       </c>
     </row>
     <row r="14">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -12232,25 +12232,25 @@
         <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2.5862</v>
+        <v>2.7273</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>4.3103</v>
+        <v>4.5455</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>2.5862</v>
+        <v>2.7273</v>
       </c>
       <c r="L14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>24.1379</v>
+        <v>23.6364</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -12259,10 +12259,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>66.3793</v>
+        <v>66.36360000000001</v>
       </c>
     </row>
     <row r="15">
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12289,25 +12289,25 @@
         <v>16</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.2727</v>
+        <v>2.2695</v>
       </c>
       <c r="H15" t="n">
         <v>13</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>1.8466</v>
+        <v>1.844</v>
       </c>
       <c r="J15" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>1.7045</v>
+        <v>1.7021</v>
       </c>
       <c r="L15" t="n">
         <v>123</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>17.4716</v>
+        <v>17.4468</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -12316,10 +12316,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>76.7045</v>
+        <v>76.7376</v>
       </c>
     </row>
     <row r="16">

--- a/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
+++ b/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="4">
@@ -658,7 +658,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -667,22 +667,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>84 (3.56%)</t>
+          <t>88 (3.96%)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>108 (4.58%)</t>
+          <t>103 (4.64%)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>92 (3.90%)</t>
+          <t>85 (3.83%)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>637 (26.99%)</t>
+          <t>601 (27.06%)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1439 (60.97%)</t>
+          <t>1344 (60.51%)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -715,22 +715,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12 (0.51%)</t>
+          <t>12 (0.54%)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>210 (8.90%)</t>
+          <t>196 (8.83%)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2114 (89.58%)</t>
+          <t>1989 (89.55%)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -763,22 +763,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51 (2.16%)</t>
+          <t>50 (2.25%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>111 (4.70%)</t>
+          <t>107 (4.82%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>45 (1.91%)</t>
+          <t>45 (2.02%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>549 (23.26%)</t>
+          <t>523 (23.55%)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1604 (67.97%)</t>
+          <t>1496 (67.36%)</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
         <v>3516</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -934,22 +934,22 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>26 (1.10%)</t>
+          <t>26 (1.17%)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>197 (8.35%)</t>
+          <t>189 (8.51%)</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2101 (89.03%)</t>
+          <t>1970 (88.70%)</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2213 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
         <v>7921</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -1058,22 +1058,22 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>20 (0.85%)</t>
+          <t>19 (0.86%)</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>10 (0.42%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>210 (8.90%)</t>
+          <t>196 (8.82%)</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2115 (89.62%)</t>
+          <t>1991 (89.64%)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         <v>445</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
+          <t>3 (0.14%)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>4 (0.18%)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
           <t>3 (0.13%)</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>4 (0.17%)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>3 (0.13%)</t>
-        </is>
-      </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>55 (2.33%)</t>
+          <t>54 (2.43%)</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2295 (97.24%)</t>
+          <t>2157 (97.12%)</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         <v>237960</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -1186,22 +1186,22 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20 (0.85%)</t>
+          <t>25 (1.13%)</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>31 (1.31%)</t>
+          <t>27 (1.22%)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>214 (9.07%)</t>
+          <t>198 (8.91%)</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2088 (88.47%)</t>
+          <t>1964 (88.43%)</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         <v>859</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1250,22 +1250,22 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
+          <t>1 (0.05%)</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>0 (0.00%)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
           <t>1 (0.04%)</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>0 (0.00%)</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>1 (0.04%)</t>
-        </is>
-      </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>18 (0.77%)</t>
+          <t>16 (0.72%)</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2340 (99.15%)</t>
+          <t>2203 (99.19%)</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>3263</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1314,22 +1314,22 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>30 (1.27%)</t>
+          <t>30 (1.35%)</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>17 (0.72%)</t>
+          <t>17 (0.77%)</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>31 (1.32%)</t>
+          <t>30 (1.35%)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>262 (11.10%)</t>
+          <t>255 (11.48%)</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2020 (85.59%)</t>
+          <t>1889 (85.05%)</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>77</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>1804</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         <v>3539</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1507,17 +1507,17 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>102 (4.32%)</t>
+          <t>95 (4.28%)</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2242 (95.00%)</t>
+          <t>2111 (95.05%)</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         <v>6084</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>9 (0.41%)</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>12 (0.51%)</t>
+          <t>11 (0.50%)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>205 (8.69%)</t>
+          <t>189 (8.51%)</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2132 (90.34%)</t>
+          <t>2011 (90.54%)</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
         <v>3686</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>52 (2.20%)</t>
+          <t>47 (2.12%)</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2307 (97.76%)</t>
+          <t>2173 (97.84%)</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>5240</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1750,22 +1750,22 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>21 (0.89%)</t>
+          <t>19 (0.86%)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>194 (8.22%)</t>
+          <t>183 (8.24%)</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2132 (90.34%)</t>
+          <t>2005 (90.27%)</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
         <v>58</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
         <v>148</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2356 (99.83%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>813</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -1942,22 +1942,22 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>13 (0.55%)</t>
+          <t>12 (0.54%)</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>101 (4.28%)</t>
+          <t>93 (4.19%)</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2238 (94.83%)</t>
+          <t>2108 (94.91%)</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
         <v>552</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>52 (2.20%)</t>
+          <t>49 (2.21%)</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2303 (97.59%)</t>
+          <t>2167 (97.57%)</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         <v>1019</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>22 (0.93%)</t>
+          <t>22 (0.99%)</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2337 (99.03%)</t>
+          <t>2198 (98.96%)</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>695</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2348 (99.49%)</t>
+          <t>2211 (99.55%)</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <v>6936</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -2190,22 +2190,22 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>17 (0.72%)</t>
+          <t>16 (0.72%)</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>13 (0.55%)</t>
+          <t>13 (0.58%)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>121 (5.13%)</t>
+          <t>117 (5.27%)</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2207 (93.52%)</t>
+          <t>2073 (93.34%)</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
         <v>6996</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -2259,17 +2259,17 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>64 (2.71%)</t>
+          <t>61 (2.75%)</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2282 (96.70%)</t>
+          <t>2146 (96.62%)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         <v>1191</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>19 (0.81%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>78 (3.30%)</t>
+          <t>72 (3.24%)</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2260 (95.76%)</t>
+          <t>2128 (95.81%)</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>560</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -2378,22 +2378,22 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>17 (0.72%)</t>
+          <t>17 (0.77%)</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>27 (1.14%)</t>
+          <t>26 (1.17%)</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>20 (0.85%)</t>
+          <t>20 (0.90%)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>188 (7.97%)</t>
+          <t>178 (8.01%)</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2108 (89.32%)</t>
+          <t>1980 (89.15%)</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         <v>1438</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>66 (2.80%)</t>
+          <t>63 (2.84%)</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>2292 (97.12%)</t>
+          <t>2156 (97.07%)</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
         <v>431</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>10 (0.42%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>2346 (99.41%)</t>
+          <t>2207 (99.37%)</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
         <v>322</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
         <v>388</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
         <v>1065</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
         <v>5</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v>7</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
         <v>77</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
         <v>75</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
         <v>241</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2213 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
         <v>288</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>17 (0.72%)</t>
+          <t>15 (0.68%)</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>2343 (99.28%)</t>
+          <t>2206 (99.32%)</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         <v>75</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
         <v>76</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         <v>75</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
         <v>75</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
         <v>75</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
         <v>75</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
         <v>247</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
         <v>1611</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -3562,22 +3562,22 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>15 (0.64%)</t>
+          <t>15 (0.68%)</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>10 (0.42%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>111 (4.70%)</t>
+          <t>102 (4.59%)</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>2219 (94.03%)</t>
+          <t>2089 (94.06%)</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
         <v>211</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
         <v>112</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>2355 (99.79%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
         <v>78</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
         <v>170</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>13 (0.55%)</t>
+          <t>13 (0.59%)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>2344 (99.32%)</t>
+          <t>2205 (99.28%)</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
         <v>2079</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>15 (0.64%)</t>
+          <t>14 (0.63%)</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>2344 (99.32%)</t>
+          <t>2206 (99.32%)</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>38</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
         <v>7645</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>121 (5.13%)</t>
+          <t>113 (5.09%)</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>2239 (94.87%)</t>
+          <t>2108 (94.91%)</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>2355 (99.79%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
         <v>98</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>14 (0.59%)</t>
+          <t>13 (0.59%)</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>2345 (99.37%)</t>
+          <t>2207 (99.37%)</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
         <v>1437</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         <v>3516</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -4258,22 +4258,22 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>18 (0.76%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>26 (1.10%)</t>
+          <t>26 (1.17%)</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>197 (8.35%)</t>
+          <t>189 (8.51%)</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>2101 (89.03%)</t>
+          <t>1970 (88.70%)</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
         <v>1789</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
         <v>23</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
         <v>35</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2213 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
         <v>2141</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>27 (1.14%)</t>
+          <t>26 (1.17%)</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>2333 (98.86%)</t>
+          <t>2195 (98.83%)</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
         <v>4220</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
         <v>1438</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>66 (2.80%)</t>
+          <t>63 (2.84%)</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>2292 (97.12%)</t>
+          <t>2156 (97.07%)</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
         <v>45</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>10 (0.42%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2350 (99.58%)</t>
+          <t>2211 (99.55%)</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
         <v>1604</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
@@ -4822,22 +4822,22 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>7 (0.32%)</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>7 (0.29%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>58 (2.46%)</t>
+          <t>55 (2.48%)</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2284 (96.78%)</t>
+          <t>2148 (96.71%)</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         <v>65</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>2354 (99.75%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
         <v>16</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v>14</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
         <v>973</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>42 (1.78%)</t>
+          <t>39 (1.76%)</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2316 (98.14%)</t>
+          <t>2180 (98.15%)</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
         <v>22</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>2355 (99.79%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
         <v>19</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         <v>556</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>7 (0.32%)</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>2352 (99.66%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
         <v>281</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>7 (0.32%)</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2352 (99.66%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
         <v>322</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
         <v>165</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
         <v>300</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
         <v>1238</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>77 (3.26%)</t>
+          <t>73 (3.29%)</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2278 (96.53%)</t>
+          <t>2143 (96.49%)</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>1065</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>3539</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -5703,17 +5703,17 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>102 (4.32%)</t>
+          <t>95 (4.28%)</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2242 (95.00%)</t>
+          <t>2111 (95.05%)</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
         <v>5</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
         <v>5</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
         <v>483</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>30 (1.27%)</t>
+          <t>29 (1.31%)</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>2327 (98.60%)</t>
+          <t>2189 (98.56%)</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
         <v>49</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>237 (10.04%)</t>
+          <t>225 (10.13%)</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2123 (89.96%)</t>
+          <t>1996 (89.87%)</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>42 (1.78%)</t>
+          <t>40 (1.80%)</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>2318 (98.22%)</t>
+          <t>2181 (98.20%)</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
         <v>13</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2213 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
         <v>219</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>20 (0.85%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>2339 (99.11%)</t>
+          <t>2202 (99.14%)</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
         <v>2383</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>11 (0.47%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2348 (99.49%)</t>
+          <t>2210 (99.50%)</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
         <v>6</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
         <v>96</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>15 (0.64%)</t>
+          <t>15 (0.68%)</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>2345 (99.36%)</t>
+          <t>2206 (99.32%)</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
         <v>1325</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
         <v>67</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>2349 (99.53%)</t>
+          <t>2210 (99.50%)</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
         <v>49</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>2352 (99.66%)</t>
+          <t>2215 (99.73%)</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
         <v>122</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>16 (0.68%)</t>
+          <t>16 (0.72%)</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>2344 (99.32%)</t>
+          <t>2205 (99.28%)</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
         <v>266</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>16 (0.68%)</t>
+          <t>15 (0.68%)</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>2341 (99.20%)</t>
+          <t>2203 (99.19%)</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
         <v>133</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
         <v>88</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
         <v>249</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>11 (0.47%)</t>
+          <t>11 (0.50%)</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>2349 (99.53%)</t>
+          <t>2210 (99.50%)</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
         <v>23</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
         <v>17</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>2354 (99.75%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         <v>87</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -7182,12 +7182,12 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>15 (0.64%)</t>
+          <t>14 (0.63%)</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>2344 (99.32%)</t>
+          <t>2206 (99.32%)</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
         <v>140</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>29 (1.23%)</t>
+          <t>28 (1.26%)</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>2329 (98.69%)</t>
+          <t>2191 (98.65%)</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
         <v>37</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
         <v>7</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         <v>52</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
         <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>7 (0.32%)</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         <v>49</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
         <v>380</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -7620,22 +7620,22 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
+          <t>1 (0.05%)</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>2 (0.09%)</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
           <t>1 (0.04%)</t>
         </is>
       </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>2 (0.09%)</t>
-        </is>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>1 (0.04%)</t>
-        </is>
-      </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>11 (0.47%)</t>
+          <t>11 (0.50%)</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>2345 (99.36%)</t>
+          <t>2206 (99.32%)</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
         <v>457</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>14 (0.59%)</t>
+          <t>14 (0.63%)</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
-          <t>2340 (99.15%)</t>
+          <t>2202 (99.14%)</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
         <v>108</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
         <v>125</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>6 (0.26%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>2353 (99.70%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
         <v>813</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -7872,22 +7872,22 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>13 (0.55%)</t>
+          <t>12 (0.54%)</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>101 (4.28%)</t>
+          <t>93 (4.19%)</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>2238 (94.83%)</t>
+          <t>2108 (94.91%)</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
         <v>3891</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>235 (9.96%)</t>
+          <t>219 (9.86%)</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>2125 (90.04%)</t>
+          <t>2002 (90.14%)</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
         <v>1375</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>23 (0.97%)</t>
+          <t>23 (1.04%)</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>219 (9.28%)</t>
+          <t>210 (9.46%)</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="N115" s="4" t="inlineStr">
         <is>
-          <t>2109 (89.36%)</t>
+          <t>1979 (89.10%)</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
         <v>195</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -8070,12 +8070,12 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>6 (0.26%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>2353 (99.70%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
         <v>75</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
         <v>241</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2213 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
         <v>288</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>17 (0.72%)</t>
+          <t>15 (0.68%)</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>2343 (99.28%)</t>
+          <t>2206 (99.32%)</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         <v>75</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
         <v>76</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
         <v>75</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
         <v>75</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
         <v>75</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
         <v>75</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
         <v>247</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
         <v>1611</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -8736,22 +8736,22 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>15 (0.64%)</t>
+          <t>15 (0.68%)</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>10 (0.42%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>111 (4.70%)</t>
+          <t>102 (4.59%)</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
-          <t>2219 (94.03%)</t>
+          <t>2089 (94.06%)</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
         <v>112</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="N128" s="4" t="inlineStr">
         <is>
-          <t>2355 (99.79%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
         <v>73</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>2356 (99.83%)</t>
+          <t>2217 (99.82%)</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8919,7 @@
         <v>112</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
         <v>107</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="N131" s="4" t="inlineStr">
         <is>
-          <t>2356 (99.83%)</t>
+          <t>2217 (99.82%)</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
         <v>122</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>9 (0.38%)</t>
+          <t>9 (0.41%)</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>2348 (99.49%)</t>
+          <t>2210 (99.50%)</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>128</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9175,7 @@
         <v>3</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         <v>114</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>2351 (99.62%)</t>
+          <t>2213 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
         <v>91</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
         <v>32</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
-          <t>2355 (99.79%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9433,7 @@
         <v>22</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
         <v>10236</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
         <v>1585</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -9570,22 +9570,22 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>30 (1.27%)</t>
+          <t>29 (1.31%)</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>100 (4.24%)</t>
+          <t>94 (4.23%)</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>2226 (94.32%)</t>
+          <t>2094 (94.28%)</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
         <v>16</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -9635,19 +9635,19 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
+          <t>1 (0.05%)</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>0 (0.00%)</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
           <t>1 (0.04%)</t>
         </is>
       </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>0 (0.00%)</t>
-        </is>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>1 (0.04%)</t>
-        </is>
-      </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
           <t>0 (0.00%)</t>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="N141" s="4" t="inlineStr">
         <is>
-          <t>2358 (99.92%)</t>
+          <t>2219 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         <v>2</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>146 (6.19%)</t>
+          <t>144 (6.48%)</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>2214 (93.81%)</t>
+          <t>2077 (93.52%)</t>
         </is>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
         <v>80</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>10 (0.42%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>2350 (99.58%)</t>
+          <t>2211 (99.55%)</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9805,7 @@
         <v>45</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>11 (0.47%)</t>
+          <t>11 (0.50%)</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>2348 (99.49%)</t>
+          <t>2209 (99.46%)</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
         <v>563</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>16 (0.68%)</t>
+          <t>14 (0.63%)</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>2337 (99.03%)</t>
+          <t>2200 (99.05%)</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
         <v>20</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
         <v>8</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="N147" s="4" t="inlineStr">
         <is>
-          <t>2355 (99.79%)</t>
+          <t>2216 (99.77%)</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10061,7 @@
         <v>77</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>2353 (99.70%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
         <v>308</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
-          <t>2357 (99.87%)</t>
+          <t>2218 (99.86%)</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
         <v>1191</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -10194,12 +10194,12 @@
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>3 (0.13%)</t>
+          <t>3 (0.14%)</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>19 (0.81%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>78 (3.30%)</t>
+          <t>72 (3.24%)</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="N150" s="4" t="inlineStr">
         <is>
-          <t>2260 (95.76%)</t>
+          <t>2128 (95.81%)</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
         <v>274</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -10263,17 +10263,17 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>19 (0.81%)</t>
+          <t>18 (0.81%)</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>2335 (98.94%)</t>
+          <t>2197 (98.92%)</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
         <v>4</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
         <v>507</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>5 (0.21%)</t>
+          <t>5 (0.23%)</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>53 (2.25%)</t>
+          <t>52 (2.34%)</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="N153" s="4" t="inlineStr">
         <is>
-          <t>2302 (97.54%)</t>
+          <t>2164 (97.43%)</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10441,7 @@
         <v>231</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -10450,22 +10450,22 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>6 (0.26%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>7 (0.30%)</t>
+          <t>7 (0.32%)</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>85 (3.60%)</t>
+          <t>80 (3.60%)</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>2256 (95.59%)</t>
+          <t>2122 (95.54%)</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
         <v>31</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>4 (0.17%)</t>
+          <t>4 (0.18%)</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>2354 (99.75%)</t>
+          <t>2215 (99.73%)</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
         <v>594</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
         <v>33</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -10652,12 +10652,12 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>11 (0.47%)</t>
+          <t>10 (0.45%)</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>2347 (99.45%)</t>
+          <t>2209 (99.46%)</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
         <v>1971</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>24 (1.02%)</t>
+          <t>22 (0.99%)</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t>2335 (98.94%)</t>
+          <t>2198 (98.96%)</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
         <v>6</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
         <v>237</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>1 (0.04%)</t>
+          <t>1 (0.05%)</t>
         </is>
       </c>
       <c r="L160" s="4" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="N160" s="4" t="inlineStr">
         <is>
-          <t>2359 (99.96%)</t>
+          <t>2220 (99.95%)</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
         <v>40</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>6 (0.25%)</t>
+          <t>6 (0.27%)</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="N161" s="4" t="inlineStr">
         <is>
-          <t>2354 (99.75%)</t>
+          <t>2215 (99.73%)</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10945,7 @@
         <v>2411</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2 (0.08%)</t>
+          <t>2 (0.09%)</t>
         </is>
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>124 (5.25%)</t>
+          <t>111 (5.00%)</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="N162" s="4" t="inlineStr">
         <is>
-          <t>2232 (94.58%)</t>
+          <t>2106 (94.82%)</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
         <v>574</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>55 (2.33%)</t>
+          <t>51 (2.30%)</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
-          <t>2305 (97.67%)</t>
+          <t>2170 (97.70%)</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11069,7 @@
         <v>1354</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -11078,22 +11078,22 @@
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>8 (0.36%)</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>17 (0.72%)</t>
+          <t>16 (0.72%)</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>14 (0.59%)</t>
+          <t>13 (0.58%)</t>
         </is>
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>159 (6.74%)</t>
+          <t>151 (6.80%)</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>2162 (91.61%)</t>
+          <t>2033 (91.54%)</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
         <v>8</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="N165" s="4" t="inlineStr">
         <is>
-          <t>2360 (100.00%)</t>
+          <t>2221 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
         <v>40</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>2360</v>
+        <v>2221</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>8 (0.34%)</t>
+          <t>7 (0.32%)</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
-          <t>2352 (99.66%)</t>
+          <t>2214 (99.68%)</t>
         </is>
       </c>
     </row>
@@ -11545,10 +11545,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -11557,10 +11557,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -11593,7 +11593,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1176</v>
+        <v>1052</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -11602,28 +11602,28 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>1.5306</v>
+        <v>1.5209</v>
       </c>
       <c r="H3" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>5.2721</v>
+        <v>5.4183</v>
       </c>
       <c r="J3" t="n">
         <v>21</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>1.7857</v>
+        <v>1.9962</v>
       </c>
       <c r="L3" t="n">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>27.9762</v>
+        <v>28.4221</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -11632,10 +11632,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>746</v>
+        <v>659</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>63.4354</v>
+        <v>62.6426</v>
       </c>
     </row>
     <row r="4">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -11662,25 +11662,25 @@
         <v>1</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.9091</v>
+        <v>0.9174</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>2.7273</v>
+        <v>2.7523</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>5.4545</v>
+        <v>5.5046</v>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>26.3636</v>
+        <v>25.6881</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -11692,7 +11692,7 @@
         <v>71</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>64.5455</v>
+        <v>65.13760000000001</v>
       </c>
     </row>
     <row r="5">
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11716,28 +11716,28 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5.5319</v>
+        <v>6.2139</v>
       </c>
       <c r="H5" t="n">
         <v>25</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>3.5461</v>
+        <v>3.6127</v>
       </c>
       <c r="J5" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>6.2411</v>
+        <v>5.6358</v>
       </c>
       <c r="L5" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>26.383</v>
+        <v>26.3006</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -11746,10 +11746,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>58.2979</v>
+        <v>58.237</v>
       </c>
     </row>
     <row r="6">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -11773,28 +11773,28 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>7.1233</v>
+        <v>7.4176</v>
       </c>
       <c r="H6" t="n">
         <v>18</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>4.9315</v>
+        <v>4.9451</v>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>5.2055</v>
+        <v>4.9451</v>
       </c>
       <c r="L6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>24.9315</v>
+        <v>24.7253</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -11806,7 +11806,7 @@
         <v>211</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>57.8082</v>
+        <v>57.967</v>
       </c>
     </row>
     <row r="7">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1176</v>
+        <v>1052</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -11896,19 +11896,19 @@
         <v>11</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.9354</v>
+        <v>1.0456</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.3401</v>
+        <v>0.3802</v>
       </c>
       <c r="L8" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>10.9694</v>
+        <v>11.0266</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -11917,10 +11917,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1032</v>
+        <v>921</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>87.7551</v>
+        <v>87.5475</v>
       </c>
     </row>
     <row r="9">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.9091</v>
+        <v>0.9174</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         <v>14</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>12.7273</v>
+        <v>12.844</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -11974,10 +11974,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>86.36360000000001</v>
+        <v>86.2385</v>
       </c>
     </row>
     <row r="10">
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -12004,25 +12004,25 @@
         <v>5</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7225</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.5674</v>
+        <v>0.578</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7225</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>6.383</v>
+        <v>6.3584</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -12031,10 +12031,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>91.63120000000001</v>
+        <v>91.6185</v>
       </c>
     </row>
     <row r="11">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -12067,19 +12067,19 @@
         <v>3</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.8219</v>
+        <v>0.8242</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5495</v>
       </c>
       <c r="L11" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>5.4795</v>
+        <v>5.4945</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -12088,10 +12088,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>93.1507</v>
+        <v>93.1319</v>
       </c>
     </row>
     <row r="12">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1176</v>
+        <v>1052</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -12172,28 +12172,28 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>1.4456</v>
+        <v>1.5209</v>
       </c>
       <c r="H13" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>6.2925</v>
+        <v>6.654</v>
       </c>
       <c r="J13" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1.7007</v>
+        <v>1.9011</v>
       </c>
       <c r="L13" t="n">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>25.2551</v>
+        <v>25.8555</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -12202,10 +12202,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>768</v>
+        <v>674</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>65.3061</v>
+        <v>64.0684</v>
       </c>
     </row>
     <row r="14">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -12232,25 +12232,25 @@
         <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2.7273</v>
+        <v>2.7523</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>4.5455</v>
+        <v>4.5872</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>2.7273</v>
+        <v>2.7523</v>
       </c>
       <c r="L14" t="n">
         <v>26</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>23.6364</v>
+        <v>23.8532</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -12259,10 +12259,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>66.36360000000001</v>
+        <v>66.05500000000001</v>
       </c>
     </row>
     <row r="15">
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12289,25 +12289,25 @@
         <v>16</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.2695</v>
+        <v>2.3121</v>
       </c>
       <c r="H15" t="n">
         <v>13</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>1.844</v>
+        <v>1.8786</v>
       </c>
       <c r="J15" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>1.7021</v>
+        <v>1.7341</v>
       </c>
       <c r="L15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>17.4468</v>
+        <v>17.6301</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -12316,10 +12316,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>76.7376</v>
+        <v>76.4451</v>
       </c>
     </row>
     <row r="16">
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -12346,25 +12346,25 @@
         <v>13</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>3.5616</v>
+        <v>3.5714</v>
       </c>
       <c r="H16" t="n">
         <v>19</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>5.2055</v>
+        <v>5.2198</v>
       </c>
       <c r="J16" t="n">
         <v>9</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>2.4658</v>
+        <v>2.4725</v>
       </c>
       <c r="L16" t="n">
         <v>102</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>27.9452</v>
+        <v>28.022</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -12373,10 +12373,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>60.8219</v>
+        <v>60.7143</v>
       </c>
     </row>
   </sheetData>

--- a/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
+++ b/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Collection summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ontology benchmark" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="H2KG branch summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ontology benchmark" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2KG branch summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Collection summary'!$A$1:$J$4</definedName>

--- a/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
+++ b/ontology_release/output/docs/benchmarks/tib_collections/h2kg_tib_manuscript_tables.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -700,22 +700,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>88 (3.96%)</t>
+          <t>88 (3.95%)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>103 (4.64%)</t>
+          <t>103 (4.63%)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>85 (3.83%)</t>
+          <t>85 (3.82%)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>601 (27.06%)</t>
+          <t>601 (27.00%)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1344 (60.51%)</t>
+          <t>1349 (60.60%)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>196 (8.82%)</t>
+          <t>196 (8.81%)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1989 (89.55%)</t>
+          <t>1994 (89.58%)</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         <v>113</v>
       </c>
       <c r="D4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -807,17 +807,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>107 (4.82%)</t>
+          <t>107 (4.81%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45 (2.03%)</t>
+          <t>45 (2.02%)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>523 (23.55%)</t>
+          <t>523 (23.50%)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1496 (67.36%)</t>
+          <t>1501 (67.43%)</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>189 (8.51%)</t>
+          <t>189 (8.49%)</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>1970 (88.70%)</t>
+          <t>1975 (88.72%)</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>2213 (99.64%)</t>
+          <t>2218 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>19 (0.86%)</t>
+          <t>19 (0.85%)</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>196 (8.82%)</t>
+          <t>196 (8.81%)</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>1991 (89.64%)</t>
+          <t>1996 (89.67%)</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>2157 (97.12%)</t>
+          <t>2162 (97.12%)</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -1287,22 +1287,22 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>25 (1.13%)</t>
+          <t>25 (1.12%)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>27 (1.22%)</t>
+          <t>27 (1.21%)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>198 (8.91%)</t>
+          <t>198 (8.89%)</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>1964 (88.43%)</t>
+          <t>1969 (88.45%)</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2203 (99.19%)</t>
+          <t>2208 (99.19%)</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>17 (0.77%)</t>
+          <t>17 (0.76%)</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>255 (11.48%)</t>
+          <t>255 (11.46%)</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>1889 (85.05%)</t>
+          <t>1894 (85.09%)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>95 (4.28%)</t>
+          <t>95 (4.27%)</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2111 (95.05%)</t>
+          <t>2116 (95.06%)</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1723,22 +1723,22 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>9 (0.41%)</t>
+          <t>9 (0.40%)</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>11 (0.50%)</t>
+          <t>11 (0.49%)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>189 (8.51%)</t>
+          <t>189 (8.49%)</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2011 (90.54%)</t>
+          <t>2016 (90.57%)</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>47 (2.12%)</t>
+          <t>47 (2.11%)</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2173 (97.84%)</t>
+          <t>2178 (97.84%)</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>19 (0.86%)</t>
+          <t>19 (0.85%)</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>183 (8.24%)</t>
+          <t>183 (8.22%)</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2005 (90.27%)</t>
+          <t>2010 (90.30%)</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>93 (4.19%)</t>
+          <t>93 (4.18%)</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2108 (94.91%)</t>
+          <t>2113 (94.92%)</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>49 (2.21%)</t>
+          <t>49 (2.20%)</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2167 (97.57%)</t>
+          <t>2172 (97.57%)</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2198 (98.96%)</t>
+          <t>2203 (98.97%)</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2211 (99.55%)</t>
+          <t>2216 (99.55%)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>13 (0.59%)</t>
+          <t>13 (0.58%)</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>117 (5.27%)</t>
+          <t>117 (5.26%)</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2073 (93.34%)</t>
+          <t>2078 (93.35%)</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>61 (2.75%)</t>
+          <t>61 (2.74%)</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2146 (96.62%)</t>
+          <t>2151 (96.63%)</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>72 (3.24%)</t>
+          <t>72 (3.23%)</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2128 (95.81%)</t>
+          <t>2133 (95.82%)</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>17 (0.77%)</t>
+          <t>17 (0.76%)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>178 (8.01%)</t>
+          <t>178 (8.00%)</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>1980 (89.15%)</t>
+          <t>1985 (89.17%)</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="I26" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>63 (2.84%)</t>
+          <t>63 (2.83%)</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>2156 (97.07%)</t>
+          <t>2161 (97.08%)</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="I27" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2207 (99.37%)</t>
+          <t>2212 (99.37%)</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="I28" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="I29" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="I31" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="I32" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="I35" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2213 (99.64%)</t>
+          <t>2218 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="I36" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>15 (0.68%)</t>
+          <t>15 (0.67%)</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>2206 (99.32%)</t>
+          <t>2211 (99.33%)</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="I37" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="I39" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="I40" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I41" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I42" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="I43" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="I44" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>15 (0.68%)</t>
+          <t>15 (0.67%)</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>102 (4.59%)</t>
+          <t>102 (4.58%)</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>2089 (94.06%)</t>
+          <t>2094 (94.07%)</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="I47" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O47" s="7" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="I48" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>13 (0.59%)</t>
+          <t>13 (0.58%)</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>2205 (99.28%)</t>
+          <t>2210 (99.28%)</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2206 (99.32%)</t>
+          <t>2211 (99.33%)</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="I50" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="I51" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>113 (5.09%)</t>
+          <t>113 (5.08%)</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>2108 (94.91%)</t>
+          <t>2113 (94.92%)</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="I52" s="7" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>13 (0.59%)</t>
+          <t>13 (0.58%)</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2207 (99.37%)</t>
+          <t>2212 (99.37%)</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>189 (8.51%)</t>
+          <t>189 (8.49%)</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>1970 (88.70%)</t>
+          <t>1975 (88.72%)</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2213 (99.64%)</t>
+          <t>2218 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2195 (98.83%)</t>
+          <t>2200 (98.83%)</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>63 (2.84%)</t>
+          <t>63 (2.83%)</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2156 (97.07%)</t>
+          <t>2161 (97.08%)</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2211 (99.55%)</t>
+          <t>2216 (99.55%)</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>55 (2.48%)</t>
+          <t>55 (2.47%)</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2148 (96.71%)</t>
+          <t>2153 (96.72%)</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>39 (1.76%)</t>
+          <t>39 (1.75%)</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2180 (98.15%)</t>
+          <t>2185 (98.16%)</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -6341,22 +6341,22 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>73 (3.29%)</t>
+          <t>73 (3.28%)</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2143 (96.49%)</t>
+          <t>2148 (96.50%)</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
@@ -6499,12 +6499,12 @@
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>95 (4.28%)</t>
+          <t>95 (4.27%)</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2111 (95.05%)</t>
+          <t>2116 (95.06%)</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
@@ -6713,12 +6713,12 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>29 (1.31%)</t>
+          <t>29 (1.30%)</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2189 (98.56%)</t>
+          <t>2194 (98.56%)</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>225 (10.13%)</t>
+          <t>225 (10.11%)</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>1996 (89.87%)</t>
+          <t>2001 (89.89%)</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2181 (98.20%)</t>
+          <t>2186 (98.20%)</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2213 (99.64%)</t>
+          <t>2218 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2202 (99.14%)</t>
+          <t>2207 (99.15%)</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2210 (99.50%)</t>
+          <t>2215 (99.51%)</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>15 (0.68%)</t>
+          <t>15 (0.67%)</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2206 (99.32%)</t>
+          <t>2211 (99.33%)</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2210 (99.50%)</t>
+          <t>2215 (99.51%)</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2215 (99.73%)</t>
+          <t>2220 (99.73%)</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2205 (99.28%)</t>
+          <t>2210 (99.28%)</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>15 (0.68%)</t>
+          <t>15 (0.67%)</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2203 (99.19%)</t>
+          <t>2208 (99.19%)</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>11 (0.50%)</t>
+          <t>11 (0.49%)</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2210 (99.50%)</t>
+          <t>2215 (99.51%)</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2206 (99.32%)</t>
+          <t>2211 (99.33%)</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2191 (98.65%)</t>
+          <t>2196 (98.65%)</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="O107" s="4" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>11 (0.50%)</t>
+          <t>11 (0.49%)</t>
         </is>
       </c>
       <c r="O109" s="4" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2206 (99.32%)</t>
+          <t>2211 (99.33%)</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="L110" s="4" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2202 (99.14%)</t>
+          <t>2207 (99.15%)</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>93 (4.19%)</t>
+          <t>93 (4.18%)</t>
         </is>
       </c>
       <c r="O113" s="4" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2108 (94.91%)</t>
+          <t>2113 (94.92%)</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>219 (9.86%)</t>
+          <t>219 (9.84%)</t>
         </is>
       </c>
       <c r="O114" s="4" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2002 (90.14%)</t>
+          <t>2007 (90.16%)</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>23 (1.04%)</t>
+          <t>23 (1.03%)</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="N115" s="4" t="inlineStr">
         <is>
-          <t>210 (9.46%)</t>
+          <t>210 (9.43%)</t>
         </is>
       </c>
       <c r="O115" s="4" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>1979 (89.10%)</t>
+          <t>1984 (89.13%)</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2213 (99.64%)</t>
+          <t>2218 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>15 (0.68%)</t>
+          <t>15 (0.67%)</t>
         </is>
       </c>
       <c r="O119" s="4" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2206 (99.32%)</t>
+          <t>2211 (99.33%)</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
@@ -10017,12 +10017,12 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>15 (0.68%)</t>
+          <t>15 (0.67%)</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
-          <t>102 (4.59%)</t>
+          <t>102 (4.58%)</t>
         </is>
       </c>
       <c r="O127" s="4" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2089 (94.06%)</t>
+          <t>2094 (94.07%)</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2217 (99.82%)</t>
+          <t>2222 (99.82%)</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2217 (99.82%)</t>
+          <t>2222 (99.82%)</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>9 (0.41%)</t>
+          <t>9 (0.40%)</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2210 (99.50%)</t>
+          <t>2215 (99.51%)</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O133" s="4" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2213 (99.64%)</t>
+          <t>2218 (99.64%)</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="O137" s="4" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="O139" s="4" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>29 (1.31%)</t>
+          <t>29 (1.30%)</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>94 (4.23%)</t>
+          <t>94 (4.22%)</t>
         </is>
       </c>
       <c r="O140" s="4" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2094 (94.28%)</t>
+          <t>2099 (94.29%)</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="N141" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O141" s="4" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2219 (99.91%)</t>
+          <t>2224 (99.91%)</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11112,7 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>144 (6.48%)</t>
+          <t>144 (6.47%)</t>
         </is>
       </c>
       <c r="O142" s="4" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2077 (93.52%)</t>
+          <t>2082 (93.53%)</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2211 (99.55%)</t>
+          <t>2216 (99.55%)</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>11 (0.50%)</t>
+          <t>11 (0.49%)</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2209 (99.46%)</t>
+          <t>2214 (99.46%)</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2200 (99.05%)</t>
+          <t>2205 (99.06%)</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11404,7 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2216 (99.77%)</t>
+          <t>2221 (99.78%)</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2218 (99.86%)</t>
+          <t>2223 (99.87%)</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>3 (0.14%)</t>
+          <t>3 (0.13%)</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="N150" s="4" t="inlineStr">
         <is>
-          <t>72 (3.24%)</t>
+          <t>72 (3.23%)</t>
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2128 (95.81%)</t>
+          <t>2133 (95.82%)</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2197 (98.92%)</t>
+          <t>2202 (98.92%)</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>5 (0.23%)</t>
+          <t>5 (0.22%)</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2164 (97.43%)</t>
+          <t>2169 (97.44%)</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>80 (3.60%)</t>
+          <t>80 (3.59%)</t>
         </is>
       </c>
       <c r="O154" s="4" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2122 (95.54%)</t>
+          <t>2127 (95.55%)</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2215 (99.73%)</t>
+          <t>2220 (99.73%)</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2209 (99.46%)</t>
+          <t>2214 (99.46%)</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="L158" s="4" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2198 (98.96%)</t>
+          <t>2203 (98.97%)</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>1 (0.05%)</t>
+          <t>1 (0.04%)</t>
         </is>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2220 (99.95%)</t>
+          <t>2225 (99.96%)</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2215 (99.73%)</t>
+          <t>2220 (99.73%)</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="N162" s="4" t="inlineStr">
         <is>
-          <t>111 (5.00%)</t>
+          <t>111 (4.99%)</t>
         </is>
       </c>
       <c r="O162" s="4" t="inlineStr">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2106 (94.82%)</t>
+          <t>2111 (94.83%)</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
-          <t>51 (2.30%)</t>
+          <t>51 (2.29%)</t>
         </is>
       </c>
       <c r="O163" s="4" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2170 (97.70%)</t>
+          <t>2175 (97.71%)</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
@@ -12739,12 +12739,12 @@
       </c>
       <c r="M164" s="4" t="inlineStr">
         <is>
-          <t>13 (0.59%)</t>
+          <t>13 (0.58%)</t>
         </is>
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>151 (6.80%)</t>
+          <t>151 (6.78%)</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2033 (91.54%)</t>
+          <t>2038 (91.55%)</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2221 (100.00%)</t>
+          <t>2226 (100.00%)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
-          <t>7 (0.32%)</t>
+          <t>7 (0.31%)</t>
         </is>
       </c>
       <c r="O166" s="4" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2214 (99.68%)</t>
+          <t>2219 (99.69%)</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -13276,25 +13276,25 @@
         <v>16</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>1.5209</v>
+        <v>1.5137</v>
       </c>
       <c r="H3" t="n">
         <v>57</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>5.4183</v>
+        <v>5.3926</v>
       </c>
       <c r="J3" t="n">
         <v>21</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>1.9962</v>
+        <v>1.9868</v>
       </c>
       <c r="L3" t="n">
         <v>299</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>28.4221</v>
+        <v>28.2876</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -13303,10 +13303,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>62.6426</v>
+        <v>62.8193</v>
       </c>
     </row>
     <row r="4">
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -13567,19 +13567,19 @@
         <v>11</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>1.0456</v>
+        <v>1.0407</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.3802</v>
+        <v>0.3784</v>
       </c>
       <c r="L8" t="n">
         <v>116</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>11.0266</v>
+        <v>10.9745</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -13588,10 +13588,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>87.5475</v>
+        <v>87.60639999999999</v>
       </c>
     </row>
     <row r="9">
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -13846,25 +13846,25 @@
         <v>16</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>1.5209</v>
+        <v>1.5137</v>
       </c>
       <c r="H13" t="n">
         <v>70</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>6.654</v>
+        <v>6.6225</v>
       </c>
       <c r="J13" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1.9011</v>
+        <v>1.8921</v>
       </c>
       <c r="L13" t="n">
         <v>272</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>25.8555</v>
+        <v>25.7332</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13873,10 +13873,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>64.0684</v>
+        <v>64.2384</v>
       </c>
     </row>
     <row r="14">
